--- a/output/Tables/2019/HIA_per_disease.xlsx
+++ b/output/Tables/2019/HIA_per_disease.xlsx
@@ -1,108 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7C984F-CA0C-E948-AB76-5A2BF160B950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="660" windowWidth="28480" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>Morbidity</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -202,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -236,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -271,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -447,83 +350,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
       </c>
       <c r="B2">
-        <v>58496.197</v>
+        <v>58930.213</v>
       </c>
       <c r="C2">
-        <v>55612.989000000001</v>
+        <v>55999.242</v>
       </c>
       <c r="D2">
-        <v>61379.951000000001</v>
+        <v>61858.765</v>
       </c>
       <c r="E2">
-        <v>604884.65800000005</v>
+        <v>606953.879</v>
       </c>
       <c r="F2">
-        <v>587117.32299999997</v>
+        <v>589013.399</v>
       </c>
       <c r="G2">
-        <v>622704.42599999998</v>
+        <v>624932.166</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -535,200 +455,210 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>80450864508.582001</v>
+        <v>80724538721.64301</v>
       </c>
       <c r="L2">
-        <v>78074500200.901001</v>
+        <v>78326420348.13499</v>
       </c>
       <c r="M2">
-        <v>82820066431.078003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
+        <v>83113563736.239</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
       </c>
       <c r="B3">
-        <v>40147.745000000003</v>
+        <v>40688.305</v>
       </c>
       <c r="C3">
-        <v>38394.953999999998</v>
+        <v>38910.706</v>
       </c>
       <c r="D3">
-        <v>41907.275000000001</v>
+        <v>42466.299</v>
       </c>
       <c r="E3">
-        <v>35940.072</v>
+        <v>36290.607</v>
       </c>
       <c r="F3">
-        <v>34538.406999999999</v>
+        <v>34861.852</v>
       </c>
       <c r="G3">
-        <v>37361.195</v>
+        <v>37720.969</v>
       </c>
       <c r="H3">
-        <v>2236285834.0949998</v>
+        <v>2266334981.756</v>
       </c>
       <c r="I3">
-        <v>2139020016.589</v>
+        <v>2168178980.309</v>
       </c>
       <c r="J3">
-        <v>2334382070.52</v>
+        <v>2365718687.565</v>
       </c>
       <c r="K3">
-        <v>4780649331.573</v>
+        <v>4826562602.992</v>
       </c>
       <c r="L3">
-        <v>4593104654.4969997</v>
+        <v>4637225333.654</v>
       </c>
       <c r="M3">
-        <v>4968855086.3430004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
+        <v>5017090935.564</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
       </c>
       <c r="B4">
-        <v>31225.536</v>
+        <v>30220.085</v>
       </c>
       <c r="C4">
-        <v>29770.931</v>
+        <v>28904.165</v>
       </c>
       <c r="D4">
-        <v>32738.557000000001</v>
+        <v>31575.116</v>
       </c>
       <c r="E4">
-        <v>47085.235999999997</v>
+        <v>45468.57</v>
       </c>
       <c r="F4">
-        <v>44414.474999999999</v>
+        <v>43052.029</v>
       </c>
       <c r="G4">
-        <v>49916.631000000001</v>
+        <v>47978.646</v>
       </c>
       <c r="H4">
-        <v>462381324.171</v>
+        <v>447508426.812</v>
       </c>
       <c r="I4">
-        <v>440895317.35600001</v>
+        <v>428064867.975</v>
       </c>
       <c r="J4">
-        <v>484837826.92900002</v>
+        <v>467616494.748</v>
       </c>
       <c r="K4">
-        <v>6262145851.1260004</v>
+        <v>6047177615.154</v>
       </c>
       <c r="L4">
-        <v>5905459759.4040003</v>
+        <v>5726233152.491</v>
       </c>
       <c r="M4">
-        <v>6636403523.8389997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
+        <v>6380177399.908</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
       </c>
       <c r="B5">
-        <v>6404.2579999999998</v>
+        <v>6467.609</v>
       </c>
       <c r="C5">
-        <v>6095.1279999999997</v>
+        <v>6183.354</v>
       </c>
       <c r="D5">
-        <v>6721.067</v>
+        <v>6755.005</v>
       </c>
       <c r="E5">
-        <v>12502.744000000001</v>
+        <v>12607.251</v>
       </c>
       <c r="F5">
-        <v>11875.522000000001</v>
+        <v>12030.088</v>
       </c>
       <c r="G5">
-        <v>13142.02</v>
+        <v>13196.69</v>
       </c>
       <c r="H5">
-        <v>481611509.22600001</v>
+        <v>486317367.227</v>
       </c>
       <c r="I5">
-        <v>458313512.26099998</v>
+        <v>464971877.035</v>
       </c>
       <c r="J5">
-        <v>505193417.324</v>
+        <v>508006739.403</v>
       </c>
       <c r="K5">
-        <v>1662860969.4000001</v>
+        <v>1676746025.067</v>
       </c>
       <c r="L5">
-        <v>1579278195.148</v>
+        <v>1599905101.52</v>
       </c>
       <c r="M5">
-        <v>1747851369.4619999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
+        <v>1754993960.629</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
       </c>
       <c r="B6">
-        <v>13936.478999999999</v>
+        <v>13945.109</v>
       </c>
       <c r="C6">
-        <v>13089.929</v>
+        <v>13101.577</v>
       </c>
       <c r="D6">
-        <v>14788.56</v>
+        <v>14795.302</v>
       </c>
       <c r="E6">
-        <v>23252.173999999999</v>
+        <v>23367.04</v>
       </c>
       <c r="F6">
-        <v>22102.18</v>
+        <v>22210.43</v>
       </c>
       <c r="G6">
-        <v>24412.370999999999</v>
+        <v>24529.575</v>
       </c>
       <c r="H6">
-        <v>234603634.648</v>
+        <v>234771043.019</v>
       </c>
       <c r="I6">
-        <v>220507915.67300001</v>
+        <v>220626062.485</v>
       </c>
       <c r="J6">
-        <v>248863397.11399999</v>
+        <v>249029071.681</v>
       </c>
       <c r="K6">
-        <v>3092645316.941</v>
+        <v>3107629932.874</v>
       </c>
       <c r="L6">
-        <v>2938681519.855</v>
+        <v>2953645151.626</v>
       </c>
       <c r="M6">
-        <v>3246848652.5970001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
+        <v>3262635905.638</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
       </c>
       <c r="B7">
-        <v>126005.061</v>
+        <v>144005.604</v>
       </c>
       <c r="C7">
-        <v>121290.152</v>
+        <v>138618.729</v>
       </c>
       <c r="D7">
-        <v>130799.503</v>
+        <v>149398.611</v>
       </c>
       <c r="E7">
-        <v>41027.608999999997</v>
+        <v>46473.555</v>
       </c>
       <c r="F7">
-        <v>38919.728000000003</v>
+        <v>44079.866</v>
       </c>
       <c r="G7">
-        <v>43216.125</v>
+        <v>48906.229</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -740,95 +670,99 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>5456849853.6190004</v>
+        <v>6181674434.198</v>
       </c>
       <c r="L7">
-        <v>5174349651.0459995</v>
+        <v>5862971748.08</v>
       </c>
       <c r="M7">
-        <v>5748665005.3710003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
+        <v>6505174068.249</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Morbidity</t>
+        </is>
       </c>
       <c r="B8">
-        <v>217719.079</v>
+        <v>235326.712</v>
       </c>
       <c r="C8">
-        <v>208641.09400000001</v>
+        <v>225718.531</v>
       </c>
       <c r="D8">
-        <v>226954.962</v>
+        <v>244990.333</v>
       </c>
       <c r="E8">
-        <v>159807.83499999999</v>
+        <v>164207.023</v>
       </c>
       <c r="F8">
-        <v>151850.31200000001</v>
+        <v>156234.265</v>
       </c>
       <c r="G8">
-        <v>168048.342</v>
+        <v>172332.109</v>
       </c>
       <c r="H8">
-        <v>3414882302.1399989</v>
+        <v>3434931818.814</v>
       </c>
       <c r="I8">
-        <v>3258736761.8790002</v>
+        <v>3281841787.804</v>
       </c>
       <c r="J8">
-        <v>3573276711.8870001</v>
+        <v>3590370993.397</v>
       </c>
       <c r="K8">
-        <v>21255151322.659</v>
+        <v>21839790610.285</v>
       </c>
       <c r="L8">
-        <v>20190873779.950001</v>
+        <v>20779980487.371</v>
       </c>
       <c r="M8">
-        <v>22348623637.612</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>20</v>
+        <v>22920072269.988</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="B9">
-        <v>276215.27600000001</v>
+        <v>294256.925</v>
       </c>
       <c r="C9">
-        <v>264254.08299999998</v>
+        <v>281717.773</v>
       </c>
       <c r="D9">
-        <v>288334.913</v>
+        <v>306849.098</v>
       </c>
       <c r="E9">
-        <v>764692.49300000002</v>
+        <v>771160.902</v>
       </c>
       <c r="F9">
-        <v>738967.63500000001</v>
+        <v>745247.664</v>
       </c>
       <c r="G9">
-        <v>790752.76800000004</v>
+        <v>797264.2749999999</v>
       </c>
       <c r="H9">
-        <v>3414882302.1399999</v>
+        <v>3434931818.814</v>
       </c>
       <c r="I9">
-        <v>3258736761.8790002</v>
+        <v>3281841787.804</v>
       </c>
       <c r="J9">
-        <v>3573276711.8870001</v>
+        <v>3590370993.397</v>
       </c>
       <c r="K9">
-        <v>101706015831.241</v>
+        <v>102564329331.928</v>
       </c>
       <c r="L9">
-        <v>98265373980.850998</v>
+        <v>99106400835.50601</v>
       </c>
       <c r="M9">
-        <v>105168690068.69</v>
+        <v>106033636006.227</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/HIA_per_disease.xlsx
+++ b/output/Tables/2019/HIA_per_disease.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>58930.213</v>
+        <v>51362.619</v>
       </c>
       <c r="C2">
-        <v>55999.242</v>
+        <v>48710.205</v>
       </c>
       <c r="D2">
-        <v>61858.765</v>
+        <v>54014.347</v>
       </c>
       <c r="E2">
-        <v>606953.879</v>
+        <v>552338.677</v>
       </c>
       <c r="F2">
-        <v>589013.399</v>
+        <v>535031.776</v>
       </c>
       <c r="G2">
-        <v>624932.166</v>
+        <v>569595.899</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>80724538721.64301</v>
+        <v>73457502643.42</v>
       </c>
       <c r="L2">
-        <v>78326420348.13499</v>
+        <v>71155118482.047</v>
       </c>
       <c r="M2">
-        <v>83113563736.239</v>
+        <v>75760832331.953</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>40688.305</v>
+        <v>35263.453</v>
       </c>
       <c r="C3">
-        <v>38910.706</v>
+        <v>33598.708</v>
       </c>
       <c r="D3">
-        <v>42466.299</v>
+        <v>36940.202</v>
       </c>
       <c r="E3">
-        <v>36290.607</v>
+        <v>48649.374</v>
       </c>
       <c r="F3">
-        <v>34861.852</v>
+        <v>46583.251</v>
       </c>
       <c r="G3">
-        <v>37720.969</v>
+        <v>50725.869</v>
       </c>
       <c r="H3">
-        <v>2266334981.756</v>
+        <v>1858242896.74</v>
       </c>
       <c r="I3">
-        <v>2168178980.309</v>
+        <v>1771234043.127</v>
       </c>
       <c r="J3">
-        <v>2365718687.565</v>
+        <v>1946112183.064</v>
       </c>
       <c r="K3">
-        <v>4826562602.992</v>
+        <v>6470852595.332</v>
       </c>
       <c r="L3">
-        <v>4637225333.654</v>
+        <v>6195729238.76</v>
       </c>
       <c r="M3">
-        <v>5017090935.564</v>
+        <v>6746669791.212</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>30220.085</v>
+        <v>8195.287</v>
       </c>
       <c r="C4">
-        <v>28904.165</v>
+        <v>7728.303</v>
       </c>
       <c r="D4">
-        <v>31575.116</v>
+        <v>8673.121999999999</v>
       </c>
       <c r="E4">
-        <v>45468.57</v>
+        <v>3858.225</v>
       </c>
       <c r="F4">
-        <v>43052.029</v>
+        <v>3653.642</v>
       </c>
       <c r="G4">
-        <v>47978.646</v>
+        <v>4068.359</v>
       </c>
       <c r="H4">
-        <v>447508426.812</v>
+        <v>240298426.653</v>
       </c>
       <c r="I4">
-        <v>428064867.975</v>
+        <v>226621167.169</v>
       </c>
       <c r="J4">
-        <v>467616494.748</v>
+        <v>254393564.532</v>
       </c>
       <c r="K4">
-        <v>6047177615.154</v>
+        <v>513168037.131</v>
       </c>
       <c r="L4">
-        <v>5726233152.491</v>
+        <v>486016076.79</v>
       </c>
       <c r="M4">
-        <v>6380177399.908</v>
+        <v>541015057.86</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>6467.609</v>
+        <v>5753.567</v>
       </c>
       <c r="C5">
-        <v>6183.354</v>
+        <v>5483.873</v>
       </c>
       <c r="D5">
-        <v>6755.005</v>
+        <v>6029.478</v>
       </c>
       <c r="E5">
-        <v>12607.251</v>
+        <v>10354.297</v>
       </c>
       <c r="F5">
-        <v>12030.088</v>
+        <v>9829.147000000001</v>
       </c>
       <c r="G5">
-        <v>13196.69</v>
+        <v>10895.875</v>
       </c>
       <c r="H5">
-        <v>486317367.227</v>
+        <v>225540438.506</v>
       </c>
       <c r="I5">
-        <v>464971877.035</v>
+        <v>214949042.464</v>
       </c>
       <c r="J5">
-        <v>508006739.403</v>
+        <v>236295616.437</v>
       </c>
       <c r="K5">
-        <v>1676746025.067</v>
+        <v>1377038111.425</v>
       </c>
       <c r="L5">
-        <v>1599905101.52</v>
+        <v>1307097656.582</v>
       </c>
       <c r="M5">
-        <v>1754993960.629</v>
+        <v>1449059982.048</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>13945.109</v>
+        <v>11679.462</v>
       </c>
       <c r="C6">
-        <v>13101.577</v>
+        <v>10914.884</v>
       </c>
       <c r="D6">
-        <v>14795.302</v>
+        <v>12454.031</v>
       </c>
       <c r="E6">
-        <v>23367.04</v>
+        <v>13311.256</v>
       </c>
       <c r="F6">
-        <v>22210.43</v>
+        <v>12424.124</v>
       </c>
       <c r="G6">
-        <v>24529.575</v>
+        <v>14209.088</v>
       </c>
       <c r="H6">
-        <v>234771043.019</v>
+        <v>194378987.174</v>
       </c>
       <c r="I6">
-        <v>220626062.485</v>
+        <v>181754627.069</v>
       </c>
       <c r="J6">
-        <v>249029071.681</v>
+        <v>207180518.78</v>
       </c>
       <c r="K6">
-        <v>3107629932.874</v>
+        <v>1770294427.892</v>
       </c>
       <c r="L6">
-        <v>2953645151.626</v>
+        <v>1651580840.204</v>
       </c>
       <c r="M6">
-        <v>3262635905.638</v>
+        <v>1890403361.696</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>144005.604</v>
+        <v>126217.084</v>
       </c>
       <c r="C7">
-        <v>138618.729</v>
+        <v>121281.478</v>
       </c>
       <c r="D7">
-        <v>149398.611</v>
+        <v>131185.28</v>
       </c>
       <c r="E7">
-        <v>46473.555</v>
+        <v>47754.347</v>
       </c>
       <c r="F7">
-        <v>44079.866</v>
+        <v>45340.174</v>
       </c>
       <c r="G7">
-        <v>48906.229</v>
+        <v>50191.991</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,56 +670,56 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>6181674434.198</v>
+        <v>6352179144.035</v>
       </c>
       <c r="L7">
-        <v>5862971748.08</v>
+        <v>6029770074.206</v>
       </c>
       <c r="M7">
-        <v>6505174068.249</v>
+        <v>6675309753.489</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>Chronic diseases</t>
         </is>
       </c>
       <c r="B8">
-        <v>235326.712</v>
+        <v>60891.76900000001</v>
       </c>
       <c r="C8">
-        <v>225718.531</v>
+        <v>57725.768</v>
       </c>
       <c r="D8">
-        <v>244990.333</v>
+        <v>64096.833</v>
       </c>
       <c r="E8">
-        <v>164207.023</v>
+        <v>76173.152</v>
       </c>
       <c r="F8">
-        <v>156234.265</v>
+        <v>72490.16399999999</v>
       </c>
       <c r="G8">
-        <v>172332.109</v>
+        <v>79899.19100000001</v>
       </c>
       <c r="H8">
-        <v>3434931818.814</v>
+        <v>2518460749.073</v>
       </c>
       <c r="I8">
-        <v>3281841787.804</v>
+        <v>2394558879.829</v>
       </c>
       <c r="J8">
-        <v>3590370993.397</v>
+        <v>2643981882.813</v>
       </c>
       <c r="K8">
-        <v>21839790610.285</v>
+        <v>10131353171.78</v>
       </c>
       <c r="L8">
-        <v>20779980487.371</v>
+        <v>9640423812.336</v>
       </c>
       <c r="M8">
-        <v>22920072269.988</v>
+        <v>10627148192.816</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>294256.925</v>
+        <v>238471.472</v>
       </c>
       <c r="C9">
-        <v>281717.773</v>
+        <v>227717.451</v>
       </c>
       <c r="D9">
-        <v>306849.098</v>
+        <v>249296.46</v>
       </c>
       <c r="E9">
-        <v>771160.902</v>
+        <v>676266.176</v>
       </c>
       <c r="F9">
-        <v>745247.664</v>
+        <v>652862.1139999999</v>
       </c>
       <c r="G9">
-        <v>797264.2749999999</v>
+        <v>699687.081</v>
       </c>
       <c r="H9">
-        <v>3434931818.814</v>
+        <v>2518460749.073</v>
       </c>
       <c r="I9">
-        <v>3281841787.804</v>
+        <v>2394558879.829</v>
       </c>
       <c r="J9">
-        <v>3590370993.397</v>
+        <v>2643981882.813</v>
       </c>
       <c r="K9">
-        <v>102564329331.928</v>
+        <v>89941034959.235</v>
       </c>
       <c r="L9">
-        <v>99106400835.50601</v>
+        <v>86825312368.58897</v>
       </c>
       <c r="M9">
-        <v>106033636006.227</v>
+        <v>93063290278.25801</v>
       </c>
     </row>
   </sheetData>
